--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -498,7 +498,6 @@
           <t>021 326 181</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Centro idraulica industriale; include vendita/assistenza utensili manuali ed elettrici, ricambi. Sede confermata anche a Kralja Držislava 28A.</t>
@@ -516,7 +515,6 @@
           <t>PODACER d.o.o.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Split</t>
@@ -532,7 +530,6 @@
           <t>021 374 949</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Veletrgovina alata i tehničke robe; rappresentante esclusivo Kaufmann per HR/BiH, partner Sola e KrenHof.</t>
@@ -612,10 +609,9 @@
           <t>021 532 570</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Import, ingrosso, dettaglio e assistenza utensili elettrici/manuali (Makita, Bosch, Rems, Fein, Hilti, Stanley); dal 1993.</t>
+          <t>Import, ingrosso, dettaglio e assistenza utensili elettrici/manuali (Makita, Bosch, Rems, Fein, Hilti, Stanley); dal 1993. [DUPLICATO — vedi anche: 2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -657,7 +653,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Distributore utensili/macchine professionali (Milwaukee, Vessel), showroom 200 mq con assistenza.</t>
+          <t>Distributore utensili/macchine professionali (Milwaukee, Vessel), showroom 200 mq con assistenza. [DUPLICATO — vedi anche: 2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Radna odjeća, strojevi i alati, oprema građevinska - vendita e noleggio.</t>
+          <t>Radna odjeća, strojevi i alati, oprema građevinska - vendita e noleggio. [DUPLICATO — vedi anche: 2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -756,7 +752,6 @@
           <t>Pavlov Alati d.o.o. (Servis-Pavlov)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Kaštel Gomilica</t>
@@ -814,7 +809,6 @@
           <t>021 203 600 (reparto utensili: 021 203 626)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>BORDERLINE: grande rivenditore generalista di materiali edili/elettrodomestici con reparto utensili dedicato e numero diretto.</t>
@@ -901,7 +895,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Concessionario/dealer ufficiale Husqvarna, vendita utensili, macchine e ferramenta.</t>
+          <t>Concessionario/dealer ufficiale Husqvarna, vendita utensili, macchine e ferramenta. [DUPLICATO — vedi anche: 2026-09-20_16_Croazia_Splitsko-dalmatinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -916,7 +910,6 @@
           <t>Kalup d.o.o.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Hrvace (Sinj)</t>
@@ -932,7 +925,6 @@
           <t>099 2047655</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Produzione, assistenza e commercio di utensili diamantati per foratura/taglio pietra-cemento-asfalto. Nota: fonte secondaria (companywall) riporta anche 021 681 900 / info@kalup.hr, non confermati incrociando altre fonti - non riportati.</t>

--- a/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_16_Croazia_Splitsko-dalmatinska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
